--- a/mode_docx_gen/pmi_mtz/mtz2_modes/МТЗ 2 ст_22.xlsx
+++ b/mode_docx_gen/pmi_mtz/mtz2_modes/МТЗ 2 ст_22.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -485,6 +485,12 @@
     <col width="20" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
+    <col width="20" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -675,52 +681,82 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvalv</t>
+          <t>SGF1_lvalh</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_lvalv</t>
+          <t>SGF2_lvalh</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_lvalv</t>
+          <t>SGF3_lvalh</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_lvalv</t>
+          <t>SGF4_lvalh</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_lvalv</t>
+          <t>SGF5_lvalh</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_lvalv</t>
+          <t>SGF6_lvalh</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>SGF7_lvalv</t>
+          <t>SGF7_lvalh</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>SGF8_lvalv</t>
+          <t>SGF8_lvalh</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>SGF9_lvalv</t>
+          <t>SGF9_lvalh</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>SGF10_lvalv</t>
+          <t>SGF10_lvalh</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptoc1_lvarctoc</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptoc1_lvarctoc</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Номинальный ток входа</t>
         </is>
       </c>
     </row>
@@ -865,6 +901,24 @@
       </c>
       <c r="AU2" t="n">
         <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -878,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -902,6 +956,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1010,34 +1065,39 @@
           <t>T1_lvrbvtr2</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc1_lvarctoc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>50</v>
@@ -1052,7 +1112,7 @@
         <v>5</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>40</v>
@@ -1061,7 +1121,7 @@
         <v>50</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>1</v>
@@ -1070,9 +1130,12 @@
         <v>50</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1494,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG2"/>
+  <dimension ref="A1:CI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1582,6 +1645,8 @@
     <col width="20" customWidth="1" min="83" max="83"/>
     <col width="20" customWidth="1" min="84" max="84"/>
     <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="20" customWidth="1" min="86" max="86"/>
+    <col width="20" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1902,110 +1967,120 @@
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>pusk_lvalv</t>
+          <t>pusk_lvalh</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
+          <t>pusk_ptoc1_lvarctoc</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>pusk_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
           <t>IAB</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dIAB</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>IBC</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dIBC</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>ICA</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dICA</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>I2</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>I0</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>UAB_ptuv1</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>UBC_ptuv1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>UCA_ptuv1</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>U2_ptuv1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>U0_ptuv1</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>U1_ptuv1</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>UAB_ptuv2</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>UBC_ptuv2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>UCA_ptuv2</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>U2_ptuv2</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>U0_ptuv2</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>U1_ptuv2</t>
         </is>
@@ -2332,107 +2407,117 @@
           <t>1</t>
         </is>
       </c>
-      <c r="BM2" s="2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BN2" s="2" t="inlineStr">
+      <c r="BP2" s="2" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="BO2" s="2" t="inlineStr">
+      <c r="BQ2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BP2" s="2" t="inlineStr">
+      <c r="BR2" s="2" t="inlineStr">
         <is>
           <t>-90.0</t>
         </is>
       </c>
-      <c r="BQ2" s="2" t="inlineStr">
+      <c r="BS2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BR2" s="2" t="inlineStr">
+      <c r="BT2" s="2" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BU2" s="2" t="inlineStr">
+      <c r="BW2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BV2" s="2" t="inlineStr">
+      <c r="BX2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="BW2" s="2" t="inlineStr">
+      <c r="BY2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="BX2" s="2" t="inlineStr">
+      <c r="BZ2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CA2" s="2" t="inlineStr">
+      <c r="CC2" s="2" t="inlineStr">
         <is>
           <t>58.0</t>
         </is>
       </c>
-      <c r="CB2" s="2" t="inlineStr">
+      <c r="CD2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="CC2" s="2" t="inlineStr">
+      <c r="CE2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="CD2" s="2" t="inlineStr">
+      <c r="CF2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CG2" s="2" t="inlineStr">
+      <c r="CI2" s="2" t="inlineStr">
         <is>
           <t>58.0</t>
         </is>
